--- a/notebooks/CalSim3DataExtractionInitFile_v2.xlsx
+++ b/notebooks/CalSim3DataExtractionInitFile_v2.xlsx
@@ -153,7 +153,7 @@
     <t>coeqwal_cs3_scenario_listing_v4.xlsx</t>
   </si>
   <si>
-    <t>E178</t>
+    <t>E181</t>
   </si>
 </sst>
 </file>

--- a/notebooks/CalSim3DataExtractionInitFile_v2.xlsx
+++ b/notebooks/CalSim3DataExtractionInitFile_v2.xlsx
@@ -153,7 +153,7 @@
     <t>coeqwal_cs3_scenario_listing_v4.xlsx</t>
   </si>
   <si>
-    <t>E181</t>
+    <t>E180</t>
   </si>
 </sst>
 </file>

--- a/notebooks/CalSim3DataExtractionInitFile_v2.xlsx
+++ b/notebooks/CalSim3DataExtractionInitFile_v2.xlsx
@@ -153,7 +153,7 @@
     <t>coeqwal_cs3_scenario_listing_v4.xlsx</t>
   </si>
   <si>
-    <t>E180</t>
+    <t>E179</t>
   </si>
 </sst>
 </file>

--- a/notebooks/CalSim3DataExtractionInitFile_v2.xlsx
+++ b/notebooks/CalSim3DataExtractionInitFile_v2.xlsx
@@ -153,7 +153,7 @@
     <t>coeqwal_cs3_scenario_listing_v4.xlsx</t>
   </si>
   <si>
-    <t>E179</t>
+    <t>E191</t>
   </si>
 </sst>
 </file>
